--- a/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T09:05:02+00:00</t>
+    <t>2025-04-24T12:12:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:12:45+00:00</t>
+    <t>2025-04-24T12:14:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:14:49+00:00</t>
+    <t>2025-04-24T12:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/PreadmissionValueSetDocumentTypeFr</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/preadmission-document-type-valueset</t>
   </si>
   <si>
     <t>Version</t>
@@ -36,7 +37,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>PreadmissionValueSetDocumentTypeFr</t>
+    <t>PreadmissionDocumentTypeFrValueSet</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:53:37+00:00</t>
+    <t>2025-04-25T09:56:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -109,6 +110,9 @@
   </si>
   <si>
     <t>System URI</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-identifier-type</t>
   </si>
   <si>
     <t>http://hl7.fr/fhir/fr/preadmission/CodeSystem/document-type-code-system</t>
@@ -417,4 +421,44 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/preadmission-document-type-valueset</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/preadmission-document-type-valueset</t>
   </si>
   <si>
     <t>Version</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T09:56:34+00:00</t>
+    <t>2025-04-25T14:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-identifier-type</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/CodeSystem/document-type-code-system</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/CodeSystem/document-type-code-system</t>
   </si>
 </sst>
 </file>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T14:29:23+00:00</t>
+    <t>2025-04-25T16:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -112,7 +112,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-mode-validation-identity</t>
   </si>
   <si>
     <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/CodeSystem/document-type-code-system</t>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/preadmission-document-type-valueset</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/preadmission-document-type-valueset</t>
   </si>
   <si>
     <t>Version</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T16:50:14+00:00</t>
+    <t>2025-04-28T06:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-mode-validation-identity</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/CodeSystem/document-type-code-system</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/CodeSystem/document-type-code-system</t>
   </si>
 </sst>
 </file>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -55,10 +55,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T06:55:35+00:00</t>
+    <t>2025-04-28T10:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -308,74 +311,76 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -394,28 +399,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -434,28 +439,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T10:41:02+00:00</t>
+    <t>2025-05-05T08:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-05T08:51:40+00:00</t>
+    <t>2025-05-06T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-valueset.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T13:54:59+00:00</t>
+    <t>2025-05-14T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -76,7 +76,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
